--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -499,16 +499,36 @@
         <v>updated_at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>df</v>
+      </c>
+      <c r="C2" t="str">
+        <v>sdf</v>
+      </c>
+      <c r="D2" t="str">
+        <v>df</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-04-23T08:35:31.395Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-04-23T08:35:31.395Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +544,23 @@
         <v>updated_at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>dsd</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-04-23T07:33:06.407Z</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-04-23T07:33:06.407Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -7,8 +7,7 @@
     <sheet name="__schema__" sheetId="2" r:id="rId2"/>
     <sheet name="feature_list" sheetId="3" r:id="rId3"/>
     <sheet name="roles" sheetId="4" r:id="rId4"/>
-    <sheet name="access_control" sheetId="5" r:id="rId5"/>
-    <sheet name="exception" sheetId="6" r:id="rId6"/>
+    <sheet name="exception" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -423,7 +422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,23 +450,15 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>access_control</v>
+        <v>exception</v>
       </c>
       <c r="B4" t="str">
-        <v>id,role,feature_list,created_at,updated_at</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>exception</v>
-      </c>
-      <c r="B5" t="str">
         <v>id,email,feature_list,created_at,updated_at</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -574,34 +565,6 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>role</v>
-      </c>
-      <c r="C1" t="str">
-        <v>feature_list</v>
-      </c>
-      <c r="D1" t="str">
-        <v>created_at</v>
-      </c>
-      <c r="E1" t="str">
-        <v>updated_at</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
         <v>email</v>
       </c>
       <c r="C1" t="str">

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -8,6 +8,7 @@
     <sheet name="feature_list" sheetId="3" r:id="rId3"/>
     <sheet name="roles" sheetId="4" r:id="rId4"/>
     <sheet name="exception" sheetId="5" r:id="rId5"/>
+    <sheet name="profile" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -422,7 +423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -456,9 +457,17 @@
         <v>id,email,feature_list,created_at,updated_at</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>profile</v>
+      </c>
+      <c r="B5" t="str">
+        <v>id,name,email,role,settings,created_at,updated_at</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,4 +591,38 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>email</v>
+      </c>
+      <c r="D1" t="str">
+        <v>role</v>
+      </c>
+      <c r="E1" t="str">
+        <v>settings</v>
+      </c>
+      <c r="F1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="G1" t="str">
+        <v>updated_at</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -415,6 +415,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
@@ -438,7 +439,7 @@
         <v>feature_list</v>
       </c>
       <c r="B2" t="str">
-        <v>id,title,icon,path,roles,created_at,updated_at</v>
+        <v>id,title,icon,path,roles,group,created_at,updated_at</v>
       </c>
     </row>
     <row r="3">
@@ -466,6 +467,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
@@ -474,7 +476,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,9 +495,12 @@
         <v>roles</v>
       </c>
       <c r="F1" t="str">
+        <v>group</v>
+      </c>
+      <c r="G1" t="str">
         <v>created_at</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>updated_at</v>
       </c>
     </row>
@@ -504,31 +509,271 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>df</v>
+        <v>Dashboard</v>
       </c>
       <c r="C2" t="str">
-        <v>sdf</v>
+        <v>Home</v>
       </c>
       <c r="D2" t="str">
-        <v>df</v>
+        <v>/home</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ADMIN,USER</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-23T08:35:31.395Z</v>
+        <v>WORK</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-04-23T08:35:31.395Z</v>
+        <v>2026-04-23T07:33:06.407Z</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-04-28T14:31:34.819Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Round Activity</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DicesIcon</v>
+      </c>
+      <c r="D3" t="str">
+        <v>/round-activity</v>
+      </c>
+      <c r="E3" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F3" t="str">
+        <v>WORK</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-04-28T14:32:40.068Z</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-04-28T14:33:39.085Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Player History</v>
+      </c>
+      <c r="C4" t="str">
+        <v>HistoryIcon</v>
+      </c>
+      <c r="D4" t="str">
+        <v>/player-history</v>
+      </c>
+      <c r="E4" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F4" t="str">
+        <v>WORK</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-04-28T14:34:05.211Z</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-04-28T14:34:05.211Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Casino Details</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Building2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>/casino-details</v>
+      </c>
+      <c r="E5" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F5" t="str">
+        <v>WORK</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-04-28T14:34:29.807Z</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-04-28T14:34:29.807Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>User Management</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Users</v>
+      </c>
+      <c r="D6" t="str">
+        <v>/user-management</v>
+      </c>
+      <c r="E6" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F6" t="str">
+        <v>WORK</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-04-28T19:40:56.394Z</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-04-28T19:42:03.071Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Template Gallery</v>
+      </c>
+      <c r="C7" t="str">
+        <v>GalleryHorizontal</v>
+      </c>
+      <c r="D7" t="str">
+        <v>/template-gallery</v>
+      </c>
+      <c r="E7" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F7" t="str">
+        <v>ASSETS</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-04-28T19:41:43.572Z</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-04-29T18:38:06.262Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Resolution Templates</v>
+      </c>
+      <c r="C8" t="str">
+        <v>FileCog</v>
+      </c>
+      <c r="D8" t="str">
+        <v>/resolution-template</v>
+      </c>
+      <c r="E8" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F8" t="str">
+        <v>TOOLS</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-04-28T19:42:47.047Z</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-04-28T19:42:47.047Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>K-Boost</v>
+      </c>
+      <c r="C9" t="str">
+        <v>BookOpen</v>
+      </c>
+      <c r="D9" t="str">
+        <v>/knowledge-boost</v>
+      </c>
+      <c r="E9" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F9" t="str">
+        <v>TOOLS</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-04-28T19:43:24.327Z</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-04-28T19:43:24.327Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Excel DB</v>
+      </c>
+      <c r="C10" t="str">
+        <v>DatabaseIcon</v>
+      </c>
+      <c r="D10" t="str">
+        <v>/excel-db</v>
+      </c>
+      <c r="E10" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F10" t="str">
+        <v>TOOLS</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-04-28T19:43:58.308Z</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2026-04-28T19:43:58.308Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Access Control</v>
+      </c>
+      <c r="C11" t="str">
+        <v>UserIcon</v>
+      </c>
+      <c r="D11" t="str">
+        <v>/access-control</v>
+      </c>
+      <c r="E11" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F11" t="str">
+        <v>TOOLS</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-04-28T19:44:33.041Z</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-04-29T13:19:56.451Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -549,18 +794,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>dsd</v>
+        <v>ADMIN</v>
       </c>
       <c r="C2" t="str">
         <v>2026-04-23T07:33:06.407Z</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23T07:33:06.407Z</v>
+        <v>2026-04-28T12:30:29.794Z</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">USER
+</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-04-28T13:44:39.072Z</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-28T13:44:39.072Z</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,6 +848,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
@@ -595,7 +857,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -620,9 +882,32 @@
         <v>updated_at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rajani</v>
+      </c>
+      <c r="C2" t="str">
+        <v>rajani.rachakonda@arrise.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-04-29T13:28:28.588Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-04-29T18:24:42.583Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -463,7 +463,7 @@
         <v>profile</v>
       </c>
       <c r="B5" t="str">
-        <v>id,name,email,role,settings,created_at,updated_at</v>
+        <v>id,name,email,role,freshdesk,settings,created_at,updated_at</v>
       </c>
     </row>
   </sheetData>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -512,7 +512,7 @@
         <v>Dashboard</v>
       </c>
       <c r="C2" t="str">
-        <v>Home</v>
+        <v>HomeIcon</v>
       </c>
       <c r="D2" t="str">
         <v>/home</v>
@@ -527,7 +527,7 @@
         <v>2026-04-23T07:33:06.407Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-04-28T14:31:34.819Z</v>
+        <v>2026-05-02T07:55:29.463Z</v>
       </c>
     </row>
     <row r="3">
@@ -648,7 +648,7 @@
         <v>/template-gallery</v>
       </c>
       <c r="E7" t="str">
-        <v>USER</v>
+        <v>USER,ADMIN</v>
       </c>
       <c r="F7" t="str">
         <v>ASSETS</v>
@@ -657,7 +657,7 @@
         <v>2026-04-28T19:41:43.572Z</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-04-29T18:38:06.262Z</v>
+        <v>2026-05-02T08:16:02.024Z</v>
       </c>
     </row>
     <row r="8">
@@ -764,9 +764,62 @@
         <v>2026-04-29T13:19:56.451Z</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Other</v>
+      </c>
+      <c r="D12" t="str">
+        <v>/profile</v>
+      </c>
+      <c r="E12" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-05-02T06:01:28.154Z</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-05-02T06:01:28.154Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Not Allowd</v>
+      </c>
+      <c r="C13" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D13" t="str">
+        <v>/not-allowd</v>
+      </c>
+      <c r="E13" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F13" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-05-02T08:01:25.792Z</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-05-02T08:01:25.792Z</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -857,7 +910,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -873,12 +926,15 @@
         <v>role</v>
       </c>
       <c r="E1" t="str">
+        <v>freshdesk</v>
+      </c>
+      <c r="F1" t="str">
         <v>settings</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>created_at</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>updated_at</v>
       </c>
     </row>
@@ -887,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Rajani</v>
+        <v>Rajani Rachakonda</v>
       </c>
       <c r="C2" t="str">
         <v>rajani.rachakonda@arrise.com</v>
@@ -896,18 +952,21 @@
         <v>ADMIN</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>U2FsdGVkX18286Us/KPbmUYKh7Kj/JAgrjWI5rcex90=</v>
       </c>
       <c r="F2" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G2" t="str">
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
-      <c r="G2" t="str">
-        <v>2026-04-29T18:24:42.583Z</v>
+      <c r="H2" t="str">
+        <v>2026-05-03T09:23:21.893Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -7,8 +7,7 @@
     <sheet name="__schema__" sheetId="2" r:id="rId2"/>
     <sheet name="feature_list" sheetId="3" r:id="rId3"/>
     <sheet name="roles" sheetId="4" r:id="rId4"/>
-    <sheet name="exception" sheetId="5" r:id="rId5"/>
-    <sheet name="profile" sheetId="6" r:id="rId6"/>
+    <sheet name="profile" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -424,7 +423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,24 +451,15 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>exception</v>
+        <v>profile</v>
       </c>
       <c r="B4" t="str">
-        <v>id,email,feature_list,created_at,updated_at</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>profile</v>
-      </c>
-      <c r="B5" t="str">
         <v>id,name,email,role,freshdesk,settings,created_at,updated_at</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -683,7 +673,7 @@
         <v>2026-04-28T19:42:47.047Z</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-04-28T19:42:47.047Z</v>
+        <v>2026-05-04T16:44:32.361Z</v>
       </c>
     </row>
     <row r="9">
@@ -817,7 +807,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
@@ -881,42 +870,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>email</v>
-      </c>
-      <c r="C1" t="str">
-        <v>feature_list</v>
-      </c>
-      <c r="D1" t="str">
-        <v>created_at</v>
-      </c>
-      <c r="E1" t="str">
-        <v>updated_at</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
         <v>name</v>
       </c>
       <c r="C1" t="str">
@@ -955,18 +915,64 @@
         <v>U2FsdGVkX18286Us/KPbmUYKh7Kj/JAgrjWI5rcex90=</v>
       </c>
       <c r="F2" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G2" t="str">
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-03T09:23:21.893Z</v>
+        <v>2026-05-04T08:59:46.843Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Saikrishna Boga</v>
+      </c>
+      <c r="C3" t="str">
+        <v>saikrishna.boga@arrise.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-05-05T12:36:15.150Z</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-05-05T12:36:15.150Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Ravindra Reddy</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ravindramprelive</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-05-05T16:15:36.777Z</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-05-05T16:15:36.777Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -414,7 +414,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
@@ -495,7 +494,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -521,7 +520,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -547,7 +546,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -573,7 +572,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -599,7 +598,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -625,7 +624,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -651,7 +650,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
       <c r="B8" t="str">
@@ -677,7 +676,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -703,7 +702,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
       <c r="B10" t="str">
@@ -729,7 +728,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
       <c r="B11" t="str">
@@ -755,7 +754,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="str">
         <v>11</v>
       </c>
       <c r="B12" t="str">
@@ -781,7 +780,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="str">
         <v>12</v>
       </c>
       <c r="B13" t="str">
@@ -832,7 +831,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -846,7 +845,7 @@
       </c>
     </row>
     <row r="3" xml:space="preserve">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
@@ -861,7 +860,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
@@ -870,7 +868,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -899,7 +897,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -921,11 +919,11 @@
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-04T08:59:46.843Z</v>
+        <v>2026-05-10T14:50:24.231Z</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -948,7 +946,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -960,9 +958,6 @@
       <c r="D4" t="str">
         <v>ADMIN</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
       <c r="G4" t="str">
         <v>2026-05-05T16:15:36.777Z</v>
       </c>
@@ -970,9 +965,23 @@
         <v>2026-05-05T16:15:36.777Z</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ravindra reddy</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ravindra.munnangi@arrise.com</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ADMIN</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -414,6 +414,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
@@ -494,7 +495,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -520,7 +521,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -546,7 +547,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -572,7 +573,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -598,7 +599,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -624,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -650,7 +651,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="str">
@@ -676,7 +677,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -702,7 +703,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="str">
@@ -728,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="str">
@@ -754,7 +755,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="str">
@@ -780,7 +781,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="str">
@@ -831,7 +832,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -845,7 +846,7 @@
       </c>
     </row>
     <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
@@ -860,6 +861,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
@@ -868,7 +870,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -897,7 +899,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -919,11 +921,11 @@
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-10T14:50:24.231Z</v>
+        <v>2026-05-04T08:59:46.843Z</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -946,42 +948,238 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
+      <c r="A4">
+        <v>5</v>
       </c>
       <c r="B4" t="str">
-        <v>Ravindra Reddy</v>
+        <v>Ravi Boss</v>
       </c>
       <c r="C4" t="str">
-        <v>ravindramprelive</v>
+        <v xml:space="preserve">ravindra.munnangi@arrise.com  </v>
       </c>
       <c r="D4" t="str">
-        <v>ADMIN</v>
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F4" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-05-05T16:15:36.777Z</v>
+        <v>2026-05-08T13:19:39.847Z</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-05-05T16:15:36.777Z</v>
+        <v>2026-05-08T13:19:39.847Z</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
+      <c r="A5">
+        <v>6</v>
       </c>
       <c r="B5" t="str">
-        <v>Ravindra reddy</v>
+        <v xml:space="preserve">Nanda </v>
       </c>
       <c r="C5" t="str">
-        <v>ravindra.munnangi@arrise.com</v>
+        <v>nandagopala.chilukuri@arrise.com</v>
       </c>
       <c r="D5" t="str">
-        <v>ADMIN</v>
+        <v>USER</v>
+      </c>
+      <c r="F5" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-05-10T21:06:00.086Z</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-05-10T21:06:13.701Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Gowtham</v>
+      </c>
+      <c r="C6" t="str">
+        <v>gowtham.ramineni@arrise.com</v>
+      </c>
+      <c r="D6" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F6" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-05-10T21:07:20.507Z</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-05-10T21:07:20.507Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Bala</v>
+      </c>
+      <c r="C7" t="str">
+        <v>balasaheb.tathe@arrise.com</v>
+      </c>
+      <c r="D7" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F7" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-05-10T21:07:57.160Z</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-05-10T21:07:57.160Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Raja</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ravipati.raja@arrise.com</v>
+      </c>
+      <c r="D8" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F8" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-05-10T21:08:52.951Z</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-05-10T21:10:15.222Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Uday</v>
+      </c>
+      <c r="C9" t="str">
+        <v>uday.mali@arrise.com</v>
+      </c>
+      <c r="D9" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F9" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-05-10T21:10:00.306Z</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-05-10T21:10:00.306Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Shirish Jaiswal</v>
+      </c>
+      <c r="C10" t="str">
+        <v>shirish.jaiswal@arrise.com</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F10" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-05-10T21:13:06.791Z</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2026-05-10T21:13:06.791Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Gaurav Khandelwal</v>
+      </c>
+      <c r="C11" t="str">
+        <v>gaurav.khandelwal@arrise.com</v>
+      </c>
+      <c r="D11" t="str">
+        <v>USER,ADMIN</v>
+      </c>
+      <c r="F11" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-05-10T21:14:01.370Z</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-05-10T21:14:01.370Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Mallikarjun Reddy V</v>
+      </c>
+      <c r="C12" t="str">
+        <v>mallikarjun.reddy@arrise.com</v>
+      </c>
+      <c r="D12" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F12" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-05-10T21:14:50.906Z</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-05-10T21:14:50.906Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Siva Tandam</v>
+      </c>
+      <c r="C13" t="str">
+        <v>siva.tandam@arrise.com</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F13" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-05-10T21:15:38.156Z</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-05-10T21:15:38.156Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -870,7 +870,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1177,9 +1177,32 @@
         <v>2026-05-10T21:15:38.156Z</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ravindramprelive</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ravindramprelive</v>
+      </c>
+      <c r="D14" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-05-10T22:01:00.676Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-05-10T22:01:15.187Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -870,7 +870,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -909,19 +909,19 @@
         <v>rajani.rachakonda@arrise.com</v>
       </c>
       <c r="D2" t="str">
-        <v>ADMIN</v>
+        <v>ADMIN,USER</v>
       </c>
       <c r="E2" t="str">
         <v>U2FsdGVkX18286Us/KPbmUYKh7Kj/JAgrjWI5rcex90=</v>
       </c>
       <c r="F2" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G2" t="str">
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-04T08:59:46.843Z</v>
+        <v>2026-05-10T22:46:30.891Z</v>
       </c>
     </row>
     <row r="3">
@@ -937,6 +937,9 @@
       <c r="D3" t="str">
         <v>ADMIN,USER</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
       <c r="F3" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
@@ -944,7 +947,7 @@
         <v>2026-05-05T12:36:15.150Z</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-05-05T12:36:15.150Z</v>
+        <v>2026-05-11T07:41:00.437Z</v>
       </c>
     </row>
     <row r="4">
@@ -961,13 +964,13 @@
         <v>ADMIN,USER</v>
       </c>
       <c r="F4" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G4" t="str">
         <v>2026-05-08T13:19:39.847Z</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-05-08T13:19:39.847Z</v>
+        <v>2026-05-10T22:44:35.455Z</v>
       </c>
     </row>
     <row r="5">
@@ -984,13 +987,13 @@
         <v>USER</v>
       </c>
       <c r="F5" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G5" t="str">
         <v>2026-05-10T21:06:00.086Z</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-10T21:06:13.701Z</v>
+        <v>2026-05-10T22:44:40.249Z</v>
       </c>
     </row>
     <row r="6">
@@ -1007,13 +1010,13 @@
         <v>USER</v>
       </c>
       <c r="F6" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G6" t="str">
         <v>2026-05-10T21:07:20.507Z</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-05-10T21:07:20.507Z</v>
+        <v>2026-05-10T22:45:50.445Z</v>
       </c>
     </row>
     <row r="7">
@@ -1029,6 +1032,9 @@
       <c r="D7" t="str">
         <v>USER</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
       <c r="F7" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>2026-05-10T21:07:57.160Z</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-05-10T21:07:57.160Z</v>
+        <v>2026-05-11T05:01:30.046Z</v>
       </c>
     </row>
     <row r="8">
@@ -1053,13 +1059,13 @@
         <v>USER</v>
       </c>
       <c r="F8" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G8" t="str">
         <v>2026-05-10T21:08:52.951Z</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-05-10T21:10:15.222Z</v>
+        <v>2026-05-10T22:45:45.333Z</v>
       </c>
     </row>
     <row r="9">
@@ -1076,13 +1082,13 @@
         <v>USER</v>
       </c>
       <c r="F9" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G9" t="str">
         <v>2026-05-10T21:10:00.306Z</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-05-10T21:10:00.306Z</v>
+        <v>2026-05-10T22:45:40.380Z</v>
       </c>
     </row>
     <row r="10">
@@ -1098,6 +1104,9 @@
       <c r="D10" t="str">
         <v>ADMIN,USER</v>
       </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
       <c r="F10" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
@@ -1105,7 +1114,7 @@
         <v>2026-05-10T21:13:06.791Z</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-05-10T21:13:06.791Z</v>
+        <v>2026-05-11T03:36:55.550Z</v>
       </c>
     </row>
     <row r="11">
@@ -1122,13 +1131,13 @@
         <v>USER,ADMIN</v>
       </c>
       <c r="F11" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G11" t="str">
         <v>2026-05-10T21:14:01.370Z</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-05-10T21:14:01.370Z</v>
+        <v>2026-05-10T22:45:13.123Z</v>
       </c>
     </row>
     <row r="12">
@@ -1145,13 +1154,13 @@
         <v>ADMIN,USER</v>
       </c>
       <c r="F12" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G12" t="str">
         <v>2026-05-10T21:14:50.906Z</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-05-10T21:14:50.906Z</v>
+        <v>2026-05-10T22:45:06.777Z</v>
       </c>
     </row>
     <row r="13">
@@ -1168,41 +1177,231 @@
         <v>ADMIN,USER</v>
       </c>
       <c r="F13" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
       <c r="G13" t="str">
         <v>2026-05-10T21:15:38.156Z</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-05-10T21:15:38.156Z</v>
+        <v>2026-05-10T22:45:02.049Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="str">
-        <v>ravindramprelive</v>
+        <v>Gaurav Khandelwal</v>
       </c>
       <c r="C14" t="str">
-        <v>ravindramprelive</v>
+        <v>gauravlive</v>
       </c>
       <c r="D14" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-05-11T05:24:50.903Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-05-11T05:25:25.605Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>17</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ramesh.komakula@arrise.com</v>
+      </c>
+      <c r="D15" t="str">
         <v>USER</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F15" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-05-11T07:38:58.963Z</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-05-11T07:45:09.741Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>18</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Amireddy</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ami.reddy@arrise.com</v>
+      </c>
+      <c r="D16" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F16" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-05-11T07:42:15.041Z</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2026-05-11T07:45:14.246Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>19</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Yasasvi</v>
+      </c>
+      <c r="C17" t="str">
+        <v>yasasvidurga.g@arrise.com</v>
+      </c>
+      <c r="D17" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F17" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-05-11T07:43:13.496Z</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2026-05-11T07:45:18.180Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>20</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Vigneshwari</v>
+      </c>
+      <c r="C18" t="str">
+        <v>vigneshwarireddy.m@arrise.com</v>
+      </c>
+      <c r="D18" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F18" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-05-11T07:44:05.061Z</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2026-05-11T07:45:24.332Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>21</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Dishil</v>
+      </c>
+      <c r="C19" t="str">
+        <v>dishil.p@arrise.com</v>
+      </c>
+      <c r="D19" t="str">
+        <v>USER</v>
+      </c>
+      <c r="E19" t="str">
         <v/>
       </c>
-      <c r="G14" t="str">
-        <v>2026-05-10T22:01:00.676Z</v>
-      </c>
-      <c r="H14" t="str">
-        <v>2026-05-10T22:01:15.187Z</v>
+      <c r="F19" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-05-11T07:44:25.215Z</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2026-05-11T09:19:32.932Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>22</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Raghavendra</v>
+      </c>
+      <c r="C20" t="str">
+        <v>raghavendra.konda@arrise.com</v>
+      </c>
+      <c r="D20" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F20" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-05-11T07:44:58.955Z</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2026-05-11T07:45:37.803Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>23</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Siva</v>
+      </c>
+      <c r="C21" t="str">
+        <v>sivatandam</v>
+      </c>
+      <c r="D21" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F21" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-05-11T09:05:01.748Z</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2026-05-11T11:31:41.750Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>24</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Tiago Moura</v>
+      </c>
+      <c r="C22" t="str">
+        <v>tiago.moura@arrise.com</v>
+      </c>
+      <c r="D22" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F22" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2026-05-11T11:31:22.511Z</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2026-05-11T11:34:26.047Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,9 +806,35 @@
         <v>2026-05-02T08:01:25.792Z</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Auditlog</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>/audit-logs</v>
+      </c>
+      <c r="E14" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Administration</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-05-13T17:40:18.760Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-05-13T18:44:33.152Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -870,7 +896,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1399,9 +1425,32 @@
         <v>2026-05-11T11:34:26.047Z</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23">
+        <v>25</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Ravindra</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ravindramlive</v>
+      </c>
+      <c r="D23" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-05-13T20:07:01.943Z</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2026-05-13T20:07:01.943Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -508,7 +508,7 @@
         <v>/home</v>
       </c>
       <c r="E2" t="str">
-        <v>ADMIN,USER</v>
+        <v>ADMIN</v>
       </c>
       <c r="F2" t="str">
         <v>WORK</v>
@@ -517,7 +517,7 @@
         <v>2026-04-23T07:33:06.407Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-02T07:55:29.463Z</v>
+        <v>2026-05-12T09:05:52.170Z</v>
       </c>
     </row>
     <row r="3">
@@ -806,35 +806,9 @@
         <v>2026-05-02T08:01:25.792Z</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Auditlog</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>/audit-logs</v>
-      </c>
-      <c r="E14" t="str">
-        <v>ADMIN</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Administration</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2026-05-13T17:40:18.760Z</v>
-      </c>
-      <c r="H14" t="str">
-        <v>2026-05-13T18:44:33.152Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -896,7 +870,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -935,19 +909,19 @@
         <v>rajani.rachakonda@arrise.com</v>
       </c>
       <c r="D2" t="str">
-        <v>ADMIN,USER</v>
+        <v>USER</v>
       </c>
       <c r="E2" t="str">
         <v>U2FsdGVkX18286Us/KPbmUYKh7Kj/JAgrjWI5rcex90=</v>
       </c>
       <c r="F2" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G2" t="str">
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-10T22:46:30.891Z</v>
+        <v>2026-05-12T10:19:42.120Z</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1240,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="str">
-        <v>Amireddy</v>
+        <v>Amireddy Satyanarayana Reddy</v>
       </c>
       <c r="C16" t="str">
         <v>ami.reddy@arrise.com</v>
@@ -1274,6 +1248,9 @@
       <c r="D16" t="str">
         <v>USER</v>
       </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
       <c r="F16" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
@@ -1281,7 +1258,7 @@
         <v>2026-05-11T07:42:15.041Z</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-05-11T07:45:14.246Z</v>
+        <v>2026-05-14T09:15:12.994Z</v>
       </c>
     </row>
     <row r="17">
@@ -1425,32 +1402,9 @@
         <v>2026-05-11T11:34:26.047Z</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23">
-        <v>25</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Ravindra</v>
-      </c>
-      <c r="C23" t="str">
-        <v>ravindramlive</v>
-      </c>
-      <c r="D23" t="str">
-        <v>USER</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v>2026-05-13T20:07:01.943Z</v>
-      </c>
-      <c r="H23" t="str">
-        <v>2026-05-13T20:07:01.943Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -508,7 +508,7 @@
         <v>/home</v>
       </c>
       <c r="E2" t="str">
-        <v>ADMIN,USER</v>
+        <v>ADMIN</v>
       </c>
       <c r="F2" t="str">
         <v>WORK</v>
@@ -517,7 +517,7 @@
         <v>2026-04-23T07:33:06.407Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-02T07:55:29.463Z</v>
+        <v>2026-05-12T09:05:52.170Z</v>
       </c>
     </row>
     <row r="3">
@@ -806,9 +806,35 @@
         <v>2026-05-02T08:01:25.792Z</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Audit Log</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Logs</v>
+      </c>
+      <c r="D14" t="str">
+        <v>/audit-logs</v>
+      </c>
+      <c r="E14" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-05-14T11:07:13.355Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-05-14T11:07:13.355Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -909,19 +935,19 @@
         <v>rajani.rachakonda@arrise.com</v>
       </c>
       <c r="D2" t="str">
-        <v>ADMIN,USER</v>
+        <v>USER</v>
       </c>
       <c r="E2" t="str">
         <v>U2FsdGVkX18286Us/KPbmUYKh7Kj/JAgrjWI5rcex90=</v>
       </c>
       <c r="F2" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G2" t="str">
         <v>2026-04-29T13:28:28.588Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-10T22:46:30.891Z</v>
+        <v>2026-05-12T10:19:42.120Z</v>
       </c>
     </row>
     <row r="3">
@@ -1240,7 +1266,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="str">
-        <v>Amireddy</v>
+        <v>Amireddy Satyanarayana Reddy</v>
       </c>
       <c r="C16" t="str">
         <v>ami.reddy@arrise.com</v>
@@ -1248,6 +1274,9 @@
       <c r="D16" t="str">
         <v>USER</v>
       </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
       <c r="F16" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
       </c>
@@ -1255,7 +1284,7 @@
         <v>2026-05-11T07:42:15.041Z</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-05-11T07:45:14.246Z</v>
+        <v>2026-05-14T09:15:12.994Z</v>
       </c>
     </row>
     <row r="17">

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -823,13 +823,13 @@
         <v>ADMIN</v>
       </c>
       <c r="F14" t="str">
-        <v>Tools</v>
+        <v>TOOLS</v>
       </c>
       <c r="G14" t="str">
         <v>2026-05-14T11:07:13.355Z</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-05-14T11:07:13.355Z</v>
+        <v>2026-05-14T11:56:03.157Z</v>
       </c>
     </row>
   </sheetData>

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -508,7 +508,7 @@
         <v>/home</v>
       </c>
       <c r="E2" t="str">
-        <v>ADMIN</v>
+        <v>ADMIN,USER</v>
       </c>
       <c r="F2" t="str">
         <v>WORK</v>
@@ -517,7 +517,7 @@
         <v>2026-04-23T07:33:06.407Z</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-12T09:05:52.170Z</v>
+        <v>2026-05-24T17:45:06.633Z</v>
       </c>
     </row>
     <row r="3">
@@ -832,9 +832,35 @@
         <v>2026-05-14T11:56:03.157Z</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Log Explorer</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>/log-exp</v>
+      </c>
+      <c r="E15" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-05-23T23:52:19.685Z</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-05-23T23:52:35.236Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -896,7 +922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -989,14 +1015,17 @@
       <c r="D4" t="str">
         <v>ADMIN,USER</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
       <c r="F4" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G4" t="str">
         <v>2026-05-08T13:19:39.847Z</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-05-10T22:44:35.455Z</v>
+        <v>2026-05-27T12:05:08.721Z</v>
       </c>
     </row>
     <row r="5">
@@ -1035,14 +1064,17 @@
       <c r="D6" t="str">
         <v>USER</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
       <c r="F6" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G6" t="str">
         <v>2026-05-10T21:07:20.507Z</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-05-10T22:45:50.445Z</v>
+        <v>2026-05-25T04:43:52.264Z</v>
       </c>
     </row>
     <row r="7">
@@ -1107,14 +1139,17 @@
       <c r="D9" t="str">
         <v>USER</v>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
       <c r="F9" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G9" t="str">
         <v>2026-05-10T21:10:00.306Z</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-05-10T22:45:40.380Z</v>
+        <v>2026-05-28T03:46:27.658Z</v>
       </c>
     </row>
     <row r="10">
@@ -1243,7 +1278,7 @@
         <v>17</v>
       </c>
       <c r="B15" t="str">
-        <v>Ramesh</v>
+        <v>Ramesh (Process)</v>
       </c>
       <c r="C15" t="str">
         <v>ramesh.komakula@arrise.com</v>
@@ -1258,7 +1293,7 @@
         <v>2026-05-11T07:38:58.963Z</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-05-11T07:45:09.741Z</v>
+        <v>2026-05-28T09:22:19.741Z</v>
       </c>
     </row>
     <row r="16">
@@ -1278,13 +1313,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
       </c>
       <c r="G16" t="str">
         <v>2026-05-11T07:42:15.041Z</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-05-14T09:15:12.994Z</v>
+        <v>2026-05-30T14:59:51.130Z</v>
       </c>
     </row>
     <row r="17">
@@ -1428,9 +1463,124 @@
         <v>2026-05-11T11:34:26.047Z</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23">
+        <v>25</v>
+      </c>
+      <c r="B23" t="str">
+        <v>rambbau</v>
+      </c>
+      <c r="C23" t="str">
+        <v>rambabu</v>
+      </c>
+      <c r="D23" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F23" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-05-25T09:40:57.758Z</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2026-05-25T09:41:20.354Z</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>26</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Teodora Moisei</v>
+      </c>
+      <c r="C24" t="str">
+        <v>teodora.moisei@pragmaticplay.com</v>
+      </c>
+      <c r="D24" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F24" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2026-05-29T13:01:02.216Z</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2026-05-29T13:30:04.113Z</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="str">
+        <v>istvan.oancea@arrise.com</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Istvan-Catalin Oancea</v>
+      </c>
+      <c r="D25" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F25" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2026-05-29T13:02:01.129Z</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2026-05-29T13:03:54.131Z</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>28</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Florentina Ursu</v>
+      </c>
+      <c r="C26" t="str">
+        <v>florentina.ursu@arrise.com</v>
+      </c>
+      <c r="D26" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F26" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2026-05-29T13:02:39.917Z</v>
+      </c>
+      <c r="H26" t="str">
+        <v>2026-05-29T13:03:58.804Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>29</v>
+      </c>
+      <c r="B27" t="str">
+        <v xml:space="preserve">Constantin-Cosmin Ularu </v>
+      </c>
+      <c r="C27" t="str">
+        <v>cosmin.ularu@arrise.com</v>
+      </c>
+      <c r="D27" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F27" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2026-05-29T13:03:28.653Z</v>
+      </c>
+      <c r="H27" t="str">
+        <v>2026-05-29T13:04:02.299Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -922,7 +922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1048,7 +1048,7 @@
         <v>2026-05-10T21:06:00.086Z</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-10T22:44:40.249Z</v>
+        <v>2026-06-03T09:24:44.347Z</v>
       </c>
     </row>
     <row r="6">
@@ -1578,9 +1578,55 @@
         <v>2026-05-29T13:04:02.299Z</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28">
+        <v>30</v>
+      </c>
+      <c r="B28" t="str">
+        <v>flores</v>
+      </c>
+      <c r="C28" t="str">
+        <v>flores</v>
+      </c>
+      <c r="D28" t="str">
+        <v>USER</v>
+      </c>
+      <c r="F28" t="str">
+        <v>{"doYouKnow":{"title":"doyouknow","on":true},"qna":{"title":"qna","on":true}}</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2026-06-03T09:24:38.136Z</v>
+      </c>
+      <c r="H28" t="str">
+        <v>2026-06-03T09:24:56.222Z</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>31</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Ravindra-prelive</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ravindramprelive</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ADMIN,USER</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>2026-06-03T10:06:34.966Z</v>
+      </c>
+      <c r="H29" t="str">
+        <v>2026-06-03T10:06:34.966Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -1166,7 +1166,7 @@
         <v>ADMIN,USER</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>U2FsdGVkX19PlyUmw3rHKvYtH0KrO5XKeyHbW2roMdnmy2rcgAYnzwvTnASx6l5d</v>
       </c>
       <c r="F10" t="str">
         <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
@@ -1175,7 +1175,7 @@
         <v>2026-05-10T21:13:06.791Z</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-05-11T03:36:55.550Z</v>
+        <v>2026-06-05T20:38:58.520Z</v>
       </c>
     </row>
     <row r="11">

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -1169,13 +1169,13 @@
         <v>U2FsdGVkX19PlyUmw3rHKvYtH0KrO5XKeyHbW2roMdnmy2rcgAYnzwvTnASx6l5d</v>
       </c>
       <c r="F10" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false},"defaultCountry":"India"}</v>
       </c>
       <c r="G10" t="str">
         <v>2026-05-10T21:13:06.791Z</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-06-05T20:38:58.520Z</v>
+        <v>2026-06-07T18:27:58.020Z</v>
       </c>
     </row>
     <row r="11">

--- a/db_storage/rbac.xlsx
+++ b/db_storage/rbac.xlsx
@@ -1016,16 +1016,16 @@
         <v>ADMIN,USER</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>U2FsdGVkX19gQwQeXqmEY7OQ6mI8kF93K6OfHfdW06UkV2ByTKI64lq5iJkLFxXH</v>
       </c>
       <c r="F4" t="str">
-        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false}}</v>
+        <v>{"doYouKnow":{"title":"doyouknow","on":false},"qna":{"title":"qna","on":false},"defaultCountry":"India"}</v>
       </c>
       <c r="G4" t="str">
         <v>2026-05-08T13:19:39.847Z</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-05-27T12:05:08.721Z</v>
+        <v>2026-06-06T10:14:32.437Z</v>
       </c>
     </row>
     <row r="5">
@@ -1175,7 +1175,7 @@
         <v>2026-05-10T21:13:06.791Z</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-06-07T18:27:58.020Z</v>
+        <v>2026-06-05T22:21:18.252Z</v>
       </c>
     </row>
     <row r="11">
